--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -310,9 +310,6 @@
   </si>
   <si>
     <t>دنگ سس</t>
-  </si>
-  <si>
-    <t>دنگ کشمش</t>
   </si>
 </sst>
 </file>
@@ -790,7 +787,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2061,21 +2058,17 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
-      </c>
-      <c r="B87" s="6">
-        <v>230000</v>
-      </c>
+        <v>3183000</v>
+      </c>
+      <c r="B87" s="6"/>
       <c r="C87" s="6"/>
-      <c r="D87" s="6" t="s">
-        <v>97</v>
-      </c>
+      <c r="D87" s="6"/>
       <c r="E87" s="3"/>
     </row>
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2085,7 +2078,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2095,7 +2088,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2105,7 +2098,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2115,7 +2108,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2125,7 +2118,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2135,7 +2128,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2145,7 +2138,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2156,7 +2149,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7331000</v>
+        <v>7101000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2168,7 +2161,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3413000</v>
+        <v>3183000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>دنگ سس</t>
+  </si>
+  <si>
+    <t>1405/07/02</t>
   </si>
 </sst>
 </file>
@@ -787,7 +790,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2058,17 +2061,23 @@
     <row r="87" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
-      </c>
-      <c r="B87" s="6"/>
+        <v>3408000</v>
+      </c>
+      <c r="B87" s="6">
+        <v>225000</v>
+      </c>
       <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="E87" s="3"/>
+      <c r="D87" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2078,7 +2087,7 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2088,7 +2097,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2098,7 +2107,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2108,7 +2117,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2118,7 +2127,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2128,7 +2137,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2138,7 +2147,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2149,7 +2158,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7101000</v>
+        <v>7326000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2161,7 +2170,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3183000</v>
+        <v>3408000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="99">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>1405/07/02</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
   </si>
 </sst>
 </file>
@@ -790,7 +793,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2077,17 +2080,23 @@
     <row r="88" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
-      </c>
-      <c r="B88" s="6"/>
+        <v>3608000</v>
+      </c>
+      <c r="B88" s="6">
+        <v>200000</v>
+      </c>
       <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
-      <c r="E88" s="3"/>
+      <c r="D88" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6"/>
@@ -2097,7 +2106,7 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2107,7 +2116,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2117,7 +2126,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2127,7 +2136,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2137,7 +2146,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2147,7 +2156,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2158,7 +2167,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7326000</v>
+        <v>7526000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2170,7 +2179,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3408000</v>
+        <v>3608000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -316,6 +316,9 @@
   </si>
   <si>
     <t>1405/07/10</t>
+  </si>
+  <si>
+    <t>1405/07/12</t>
   </si>
 </sst>
 </file>
@@ -793,7 +796,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2096,17 +2099,23 @@
     <row r="89" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="E89" s="3"/>
+      <c r="C89" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B90" s="6"/>
       <c r="C90" s="6"/>
@@ -2116,7 +2125,7 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2126,7 +2135,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2136,7 +2145,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2146,7 +2155,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2156,7 +2165,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2171,7 +2180,7 @@
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
-        <v>3918000</v>
+        <v>4918000</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
@@ -2179,7 +2188,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3608000</v>
+        <v>2608000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="102">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -319,6 +319,12 @@
   </si>
   <si>
     <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>1405/07/14</t>
+  </si>
+  <si>
+    <t>سیگار</t>
   </si>
 </sst>
 </file>
@@ -796,7 +802,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2115,17 +2121,23 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
-      </c>
-      <c r="B90" s="6"/>
+        <v>2648000</v>
+      </c>
+      <c r="B90" s="6">
+        <v>40000</v>
+      </c>
       <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="3"/>
+      <c r="D90" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2135,7 +2147,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2145,7 +2157,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2155,7 +2167,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2165,7 +2177,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2176,7 +2188,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7526000</v>
+        <v>7566000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2188,7 +2200,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2608000</v>
+        <v>2648000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -319,12 +319,6 @@
   </si>
   <si>
     <t>1405/07/12</t>
-  </si>
-  <si>
-    <t>1405/07/14</t>
-  </si>
-  <si>
-    <t>سیگار</t>
   </si>
 </sst>
 </file>
@@ -802,7 +796,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2121,23 +2115,17 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
-      </c>
-      <c r="B90" s="6">
-        <v>40000</v>
-      </c>
+        <v>2608000</v>
+      </c>
+      <c r="B90" s="6"/>
       <c r="C90" s="6"/>
-      <c r="D90" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="D90" s="6"/>
+      <c r="E90" s="3"/>
     </row>
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2147,7 +2135,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2157,7 +2145,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2167,7 +2155,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2177,7 +2165,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2188,7 +2176,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7566000</v>
+        <v>7526000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2200,7 +2188,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2648000</v>
+        <v>2608000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="101">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -319,6 +319,9 @@
   </si>
   <si>
     <t>1405/07/12</t>
+  </si>
+  <si>
+    <t>1405/07/17</t>
   </si>
 </sst>
 </file>
@@ -796,7 +799,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2115,17 +2118,23 @@
     <row r="90" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
-      </c>
-      <c r="B90" s="6"/>
+        <v>2833000</v>
+      </c>
+      <c r="B90" s="6">
+        <v>225000</v>
+      </c>
       <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
-      <c r="E90" s="3"/>
+      <c r="D90" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B91" s="6"/>
       <c r="C91" s="6"/>
@@ -2135,7 +2144,7 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2145,7 +2154,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2155,7 +2164,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2165,7 +2174,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2176,7 +2185,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7526000</v>
+        <v>7751000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2188,7 +2197,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2608000</v>
+        <v>2833000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -322,6 +322,12 @@
   </si>
   <si>
     <t>1405/07/17</t>
+  </si>
+  <si>
+    <t>1405/07/23</t>
+  </si>
+  <si>
+    <t>دنگ مزه پل دوآب</t>
   </si>
 </sst>
 </file>
@@ -799,7 +805,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2134,17 +2140,23 @@
     <row r="91" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
-      </c>
-      <c r="B91" s="6"/>
+        <v>3022000</v>
+      </c>
+      <c r="B91" s="6">
+        <v>189000</v>
+      </c>
       <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
-      <c r="E91" s="3"/>
+      <c r="D91" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="B92" s="6"/>
       <c r="C92" s="6"/>
@@ -2154,7 +2166,7 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2164,7 +2176,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2174,7 +2186,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2185,7 +2197,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7751000</v>
+        <v>7940000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2197,7 +2209,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2833000</v>
+        <v>3022000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="104">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>دنگ مزه پل دوآب</t>
+  </si>
+  <si>
+    <t>1405/07/25</t>
   </si>
 </sst>
 </file>
@@ -805,7 +808,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2156,17 +2159,23 @@
     <row r="92" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <f t="shared" si="3"/>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="3"/>
+      <c r="C92" s="6">
+        <v>189000</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="B93" s="6"/>
       <c r="C93" s="6"/>
@@ -2176,7 +2185,7 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2186,7 +2195,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2201,7 +2210,7 @@
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
-        <v>4918000</v>
+        <v>5107000</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
@@ -2209,7 +2218,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3022000</v>
+        <v>2833000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="105">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>1405/07/25</t>
+  </si>
+  <si>
+    <t>1405/07/29</t>
   </si>
 </sst>
 </file>
@@ -808,7 +811,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2833000</v>
+        <v>3103000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2175,17 +2178,23 @@
     <row r="93" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
-      </c>
-      <c r="B93" s="6"/>
+        <v>3103000</v>
+      </c>
+      <c r="B93" s="6">
+        <v>270000</v>
+      </c>
       <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
-      <c r="E93" s="3"/>
+      <c r="D93" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3103000</v>
       </c>
       <c r="B94" s="6"/>
       <c r="C94" s="6"/>
@@ -2195,7 +2204,7 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2833000</v>
+        <v>3103000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2206,7 +2215,7 @@
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>7940000</v>
+        <v>8210000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2218,7 +2227,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2833000</v>
+        <v>3103000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="106">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>1405/07/29</t>
+  </si>
+  <si>
+    <t>1405/07/30</t>
   </si>
 </sst>
 </file>
@@ -811,7 +814,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>3103000</v>
+        <v>2103000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2194,17 +2197,23 @@
     <row r="94" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <f t="shared" si="3"/>
-        <v>3103000</v>
+        <v>2103000</v>
       </c>
       <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
-      <c r="E94" s="3"/>
+      <c r="C94" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>3103000</v>
+        <v>2103000</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2219,7 +2228,7 @@
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
-        <v>5107000</v>
+        <v>6107000</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
@@ -2227,7 +2236,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>3103000</v>
+        <v>2103000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="107">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>1405/07/30</t>
+  </si>
+  <si>
+    <t>1405/08/04</t>
   </si>
 </sst>
 </file>
@@ -814,7 +817,7 @@
       </c>
       <c r="H2" s="9">
         <f>A97</f>
-        <v>2103000</v>
+        <v>2238000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2213,18 +2216,24 @@
     <row r="95" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <f t="shared" si="3"/>
-        <v>2103000</v>
-      </c>
-      <c r="B95" s="6"/>
+        <v>2238000</v>
+      </c>
+      <c r="B95" s="6">
+        <v>135000</v>
+      </c>
       <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
-      <c r="E95" s="3"/>
+      <c r="D95" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="96" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="7"/>
       <c r="B96" s="7">
         <f>SUM(B77:B95)+B71</f>
-        <v>8210000</v>
+        <v>8345000</v>
       </c>
       <c r="C96" s="7">
         <f>SUM(C77:C95)+C71</f>
@@ -2236,7 +2245,7 @@
     <row r="97" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="10">
         <f>A95</f>
-        <v>2103000</v>
+        <v>2238000</v>
       </c>
       <c r="B97" s="10"/>
       <c r="C97" s="11" t="s">

--- a/customers/danial.xlsx
+++ b/customers/danial.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="109">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -340,6 +340,12 @@
   </si>
   <si>
     <t>1405/08/04</t>
+  </si>
+  <si>
+    <t>1405/08/07</t>
+  </si>
+  <si>
+    <t>دنگ ودکا</t>
   </si>
 </sst>
 </file>
@@ -447,7 +453,21 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -816,8 +836,8 @@
         <v>1</v>
       </c>
       <c r="H2" s="9">
-        <f>A97</f>
-        <v>2238000</v>
+        <f>A122</f>
+        <v>2363000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2266,35 +2286,270 @@
       <c r="E98" s="4"/>
     </row>
     <row r="99" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="6">
+        <f>B102-C102+A97</f>
+        <v>2363000</v>
+      </c>
+      <c r="B102" s="6">
+        <v>125000</v>
+      </c>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="6">
+        <f>A102+B103-C103</f>
+        <v>2363000</v>
+      </c>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="6">
+        <f t="shared" ref="A104:A120" si="4">A103+B104-C104</f>
+        <v>2363000</v>
+      </c>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B106" s="6"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6"/>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B111" s="6"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="6"/>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B112" s="6"/>
+      <c r="C112" s="6"/>
+      <c r="D112" s="6"/>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B113" s="6"/>
+      <c r="C113" s="6"/>
+      <c r="D113" s="6"/>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B114" s="6"/>
+      <c r="C114" s="6"/>
+      <c r="D114" s="6"/>
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B115" s="6"/>
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B116" s="6"/>
+      <c r="C116" s="6"/>
+      <c r="D116" s="6"/>
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B117" s="6"/>
+      <c r="C117" s="6"/>
+      <c r="D117" s="6"/>
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B118" s="6"/>
+      <c r="C118" s="6"/>
+      <c r="D118" s="6"/>
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A119" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A120" s="6">
+        <f t="shared" si="4"/>
+        <v>2363000</v>
+      </c>
+      <c r="B120" s="6"/>
+      <c r="C120" s="6"/>
+      <c r="D120" s="6"/>
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A121" s="7"/>
+      <c r="B121" s="7">
+        <f>SUM(B102:B120)+B96</f>
+        <v>8470000</v>
+      </c>
+      <c r="C121" s="7">
+        <f>SUM(C102:C120)+C96</f>
+        <v>6107000</v>
+      </c>
+      <c r="D121" s="7"/>
+      <c r="E121" s="5"/>
+    </row>
+    <row r="122" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A122" s="10">
+        <f>A120</f>
+        <v>2363000</v>
+      </c>
+      <c r="B122" s="10"/>
+      <c r="C122" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" s="11"/>
+      <c r="E122" s="4"/>
+    </row>
+    <row r="123" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A123" s="8"/>
+      <c r="B123" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="8"/>
+      <c r="D123" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E123" s="4"/>
+    </row>
+    <row r="124" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="125" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="126" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="C122:D122"/>
     <mergeCell ref="A97:B97"/>
     <mergeCell ref="C97:D97"/>
     <mergeCell ref="C23:D23"/>
@@ -2305,14 +2560,22 @@
     <mergeCell ref="C72:D72"/>
   </mergeCells>
   <conditionalFormatting sqref="A23:B23">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="lessThanOrEqual">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A47:B47">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="lessThanOrEqual">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A72:B72">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -2320,7 +2583,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A72:B72">
+  <conditionalFormatting sqref="A97:B97">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
@@ -2328,7 +2591,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A97:B97">
+  <conditionalFormatting sqref="A122:B122">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
